--- a/DesignTable/Data/Table/Tables/buff.xlsx
+++ b/DesignTable/Data/Table/Tables/buff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5862163C-6C1C-44F8-8755-1901F8B35315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A87E8A1A-053C-437F-A752-988FDD0AAD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22365" yWindow="1065" windowWidth="21600" windowHeight="12570" xr2:uid="{6AF2622E-310D-4A72-AFF4-F431EFCED8B8}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6AF2622E-310D-4A72-AFF4-F431EFCED8B8}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>buff_Id</t>
   </si>
   <si>
@@ -98,111 +94,116 @@
     <t>buff_interval</t>
   </si>
   <si>
+    <t>buff_arg1</t>
+  </si>
+  <si>
+    <t>buff_arg2</t>
+  </si>
+  <si>
+    <t>buff_arg3</t>
+  </si>
+  <si>
+    <t>buff_arg4</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>buff_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff_duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>buff_usePercent</t>
-  </si>
-  <si>
-    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>buff_arg1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>buff_arg2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>buff_arg3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>buff_arg4</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>buff_Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_duration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>buff_usePercent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_arg1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_arg2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_arg3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff_arg4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
 </sst>
 </file>
@@ -259,7 +260,10 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -302,7 +306,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="buff">
         <xsd:complexType>
@@ -317,6 +321,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -340,7 +345,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="buff_맵" RootElement="buff" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -348,32 +353,32 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{59AB2352-79C1-4898-A7C2-C3B83364A093}" name="표2" displayName="표2" ref="A1:I7" tableType="xml" totalsRowShown="0">
   <autoFilter ref="A1:I7" xr:uid="{59AB2352-79C1-4898-A7C2-C3B83364A093}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{A8497A82-7ABB-457B-B0D5-CF71B3868DC7}" uniqueName="buff_Id" name="buff_Id" dataDxfId="8">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_Id" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{B378F151-E02E-42B1-B6D9-00FA69E0A482}" uniqueName="buff_type" name="buff_type" dataDxfId="7">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_type" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{2D52C4E8-5B65-4B43-9891-DD22B8FE3896}" uniqueName="buff_duration" name="buff_duration" dataDxfId="6">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_duration" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{3ED088B1-9FFA-4509-BCA4-B27DC5E406D1}" uniqueName="buff_interval" name="buff_interval" dataDxfId="5">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_interval" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{BB001A5B-B5A6-49D5-A2B7-2768BC17F14D}" uniqueName="buff_usePercent" name="buff_usePercent" dataDxfId="4">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{8B2EEC6C-4F2D-4F57-9F8E-F764BC98381C}" uniqueName="buff_arg1" name="buff_arg1" dataDxfId="3">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{88472642-B1A4-4F38-A0DB-06E6ECD50453}" uniqueName="buff_arg2" name="buff_arg2" dataDxfId="2">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{F7939C35-58B2-4B3A-A663-54DB3BB61AE7}" uniqueName="buff_arg3" name="buff_arg3" dataDxfId="1">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{72D9C74E-D496-4AC8-ABDA-F593C0B2E7F3}" uniqueName="buff_arg4" name="buff_arg4" dataDxfId="0">
-      <xmlColumnPr mapId="1" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
+    <tableColumn id="1" xr3:uid="{A8497A82-7ABB-457B-B0D5-CF71B3868DC7}" uniqueName="buff_Id" name="buff_Id" dataDxfId="9">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_Id" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{B378F151-E02E-42B1-B6D9-00FA69E0A482}" uniqueName="buff_type" name="buff_type" dataDxfId="8">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_type" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{2D52C4E8-5B65-4B43-9891-DD22B8FE3896}" uniqueName="buff_duration" name="buff_duration" dataDxfId="7">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_duration" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{3ED088B1-9FFA-4509-BCA4-B27DC5E406D1}" uniqueName="buff_interval" name="buff_interval" dataDxfId="6">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_interval" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{BB001A5B-B5A6-49D5-A2B7-2768BC17F14D}" uniqueName="buff_usePercent" name="buff_usePercent" dataDxfId="5">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{8B2EEC6C-4F2D-4F57-9F8E-F764BC98381C}" uniqueName="buff_arg1" name="buff_arg1" dataDxfId="4">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{88472642-B1A4-4F38-A0DB-06E6ECD50453}" uniqueName="buff_arg2" name="buff_arg2" dataDxfId="3">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{F7939C35-58B2-4B3A-A663-54DB3BB61AE7}" uniqueName="buff_arg3" name="buff_arg3" dataDxfId="2">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{72D9C74E-D496-4AC8-ABDA-F593C0B2E7F3}" uniqueName="buff_arg4" name="buff_arg4" dataDxfId="1">
+      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -381,35 +386,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}" name="표1" displayName="표1" ref="A1:I10" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I10" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}" name="표1" displayName="표1" ref="A1:J10" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J10" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05011FDA-4F14-41C5-AC4C-68F2C492A422}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{73B4F9BD-FDF4-4B4E-8E59-FBE39BB766D7}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{E5936DDB-E02E-4932-9A8C-94F211362402}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{E721F7EF-CCC2-4553-8D5D-84FB8AD34CE0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0540E44B-B507-4B33-9574-27F6747C2A66}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{E8F53B9F-BFC1-4EDA-8C37-3EF3F20F199C}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1A1BFDCF-1304-44CD-8B43-44412EA759C0}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D2A45F3D-4BD5-4F2A-A8CE-47A823FE7268}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{8329F5DD-E185-497F-B609-540FB465B139}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/buff/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{8329F5DD-E185-497F-B609-540FB465B139}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{976A6637-1B4B-43C7-B51C-C9818508FF58}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/buff/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -715,208 +723,215 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4BEC1A-52B1-461E-BFBF-FA5E0A0832C9}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -930,10 +945,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F85DA1-BCA3-4302-B43C-3D546A11E4E9}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,267 +981,297 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1014</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
         <v>1014</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
         <v>1014</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1">
         <v>1014</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1">
         <v>1014</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="1">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="1">
         <v>1014</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/buff.xlsx
+++ b/DesignTable/Data/Table/Tables/buff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A87E8A1A-053C-437F-A752-988FDD0AAD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE5848E8-7DB3-4B17-9385-3AB2F952222D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6AF2622E-310D-4A72-AFF4-F431EFCED8B8}"/>
   </bookViews>
@@ -345,7 +345,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -354,31 +354,31 @@
   <autoFilter ref="A1:I7" xr:uid="{59AB2352-79C1-4898-A7C2-C3B83364A093}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8497A82-7ABB-457B-B0D5-CF71B3868DC7}" uniqueName="buff_Id" name="buff_Id" dataDxfId="9">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{B378F151-E02E-42B1-B6D9-00FA69E0A482}" uniqueName="buff_type" name="buff_type" dataDxfId="8">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{2D52C4E8-5B65-4B43-9891-DD22B8FE3896}" uniqueName="buff_duration" name="buff_duration" dataDxfId="7">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_duration" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_duration" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{3ED088B1-9FFA-4509-BCA4-B27DC5E406D1}" uniqueName="buff_interval" name="buff_interval" dataDxfId="6">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_interval" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_interval" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{BB001A5B-B5A6-49D5-A2B7-2768BC17F14D}" uniqueName="buff_usePercent" name="buff_usePercent" dataDxfId="5">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{8B2EEC6C-4F2D-4F57-9F8E-F764BC98381C}" uniqueName="buff_arg1" name="buff_arg1" dataDxfId="4">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{88472642-B1A4-4F38-A0DB-06E6ECD50453}" uniqueName="buff_arg2" name="buff_arg2" dataDxfId="3">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{F7939C35-58B2-4B3A-A663-54DB3BB61AE7}" uniqueName="buff_arg3" name="buff_arg3" dataDxfId="2">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{72D9C74E-D496-4AC8-ABDA-F593C0B2E7F3}" uniqueName="buff_arg4" name="buff_arg4" dataDxfId="1">
-      <xmlColumnPr mapId="4" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -390,34 +390,34 @@
   <autoFilter ref="A1:J10" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05011FDA-4F14-41C5-AC4C-68F2C492A422}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{73B4F9BD-FDF4-4B4E-8E59-FBE39BB766D7}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{E5936DDB-E02E-4932-9A8C-94F211362402}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{E721F7EF-CCC2-4553-8D5D-84FB8AD34CE0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0540E44B-B507-4B33-9574-27F6747C2A66}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{E8F53B9F-BFC1-4EDA-8C37-3EF3F20F199C}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1A1BFDCF-1304-44CD-8B43-44412EA759C0}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D2A45F3D-4BD5-4F2A-A8CE-47A823FE7268}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{8329F5DD-E185-497F-B609-540FB465B139}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{976A6637-1B4B-43C7-B51C-C9818508FF58}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/buff/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/buff/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/buff.xlsx
+++ b/DesignTable/Data/Table/Tables/buff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE5848E8-7DB3-4B17-9385-3AB2F952222D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C8DE6A-F49A-44FF-8B01-A35B36FD4E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6AF2622E-310D-4A72-AFF4-F431EFCED8B8}"/>
   </bookViews>
@@ -345,7 +345,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -354,31 +354,31 @@
   <autoFilter ref="A1:I7" xr:uid="{59AB2352-79C1-4898-A7C2-C3B83364A093}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8497A82-7ABB-457B-B0D5-CF71B3868DC7}" uniqueName="buff_Id" name="buff_Id" dataDxfId="9">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{B378F151-E02E-42B1-B6D9-00FA69E0A482}" uniqueName="buff_type" name="buff_type" dataDxfId="8">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{2D52C4E8-5B65-4B43-9891-DD22B8FE3896}" uniqueName="buff_duration" name="buff_duration" dataDxfId="7">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_duration" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_duration" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{3ED088B1-9FFA-4509-BCA4-B27DC5E406D1}" uniqueName="buff_interval" name="buff_interval" dataDxfId="6">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_interval" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_interval" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{BB001A5B-B5A6-49D5-A2B7-2768BC17F14D}" uniqueName="buff_usePercent" name="buff_usePercent" dataDxfId="5">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{8B2EEC6C-4F2D-4F57-9F8E-F764BC98381C}" uniqueName="buff_arg1" name="buff_arg1" dataDxfId="4">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{88472642-B1A4-4F38-A0DB-06E6ECD50453}" uniqueName="buff_arg2" name="buff_arg2" dataDxfId="3">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{F7939C35-58B2-4B3A-A663-54DB3BB61AE7}" uniqueName="buff_arg3" name="buff_arg3" dataDxfId="2">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{72D9C74E-D496-4AC8-ABDA-F593C0B2E7F3}" uniqueName="buff_arg4" name="buff_arg4" dataDxfId="1">
-      <xmlColumnPr mapId="6" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -390,34 +390,34 @@
   <autoFilter ref="A1:J10" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05011FDA-4F14-41C5-AC4C-68F2C492A422}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{73B4F9BD-FDF4-4B4E-8E59-FBE39BB766D7}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{E5936DDB-E02E-4932-9A8C-94F211362402}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{E721F7EF-CCC2-4553-8D5D-84FB8AD34CE0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0540E44B-B507-4B33-9574-27F6747C2A66}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{E8F53B9F-BFC1-4EDA-8C37-3EF3F20F199C}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1A1BFDCF-1304-44CD-8B43-44412EA759C0}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D2A45F3D-4BD5-4F2A-A8CE-47A823FE7268}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{8329F5DD-E185-497F-B609-540FB465B139}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{976A6637-1B4B-43C7-B51C-C9818508FF58}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/buff/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/buff/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/buff.xlsx
+++ b/DesignTable/Data/Table/Tables/buff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C8DE6A-F49A-44FF-8B01-A35B36FD4E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94AE1644-F8DE-43CF-A2BE-E48E1F6BCF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6AF2622E-310D-4A72-AFF4-F431EFCED8B8}"/>
   </bookViews>
@@ -345,7 +345,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="buff_맵" RootElement="buff" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -354,31 +354,31 @@
   <autoFilter ref="A1:I7" xr:uid="{59AB2352-79C1-4898-A7C2-C3B83364A093}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8497A82-7ABB-457B-B0D5-CF71B3868DC7}" uniqueName="buff_Id" name="buff_Id" dataDxfId="9">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{B378F151-E02E-42B1-B6D9-00FA69E0A482}" uniqueName="buff_type" name="buff_type" dataDxfId="8">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{2D52C4E8-5B65-4B43-9891-DD22B8FE3896}" uniqueName="buff_duration" name="buff_duration" dataDxfId="7">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_duration" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_duration" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{3ED088B1-9FFA-4509-BCA4-B27DC5E406D1}" uniqueName="buff_interval" name="buff_interval" dataDxfId="6">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_interval" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_interval" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{BB001A5B-B5A6-49D5-A2B7-2768BC17F14D}" uniqueName="buff_usePercent" name="buff_usePercent" dataDxfId="5">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_usePercent" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{8B2EEC6C-4F2D-4F57-9F8E-F764BC98381C}" uniqueName="buff_arg1" name="buff_arg1" dataDxfId="4">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_arg1" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{88472642-B1A4-4F38-A0DB-06E6ECD50453}" uniqueName="buff_arg2" name="buff_arg2" dataDxfId="3">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_arg2" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{F7939C35-58B2-4B3A-A663-54DB3BB61AE7}" uniqueName="buff_arg3" name="buff_arg3" dataDxfId="2">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_arg3" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{72D9C74E-D496-4AC8-ABDA-F593C0B2E7F3}" uniqueName="buff_arg4" name="buff_arg4" dataDxfId="1">
-      <xmlColumnPr mapId="8" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/record/buff_arg4" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -390,34 +390,34 @@
   <autoFilter ref="A1:J10" xr:uid="{30FD2959-C189-4A09-B166-D43E2B120A85}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05011FDA-4F14-41C5-AC4C-68F2C492A422}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{73B4F9BD-FDF4-4B4E-8E59-FBE39BB766D7}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{E5936DDB-E02E-4932-9A8C-94F211362402}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{E721F7EF-CCC2-4553-8D5D-84FB8AD34CE0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0540E44B-B507-4B33-9574-27F6747C2A66}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{E8F53B9F-BFC1-4EDA-8C37-3EF3F20F199C}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1A1BFDCF-1304-44CD-8B43-44412EA759C0}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D2A45F3D-4BD5-4F2A-A8CE-47A823FE7268}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{8329F5DD-E185-497F-B609-540FB465B139}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{976A6637-1B4B-43C7-B51C-C9818508FF58}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/buff/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/buff/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
